--- a/ExportExcel/Delete Academic Degrees Test.xlsx
+++ b/ExportExcel/Delete Academic Degrees Test.xlsx
@@ -41,7 +41,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>1845 ms</t>
+    <t>2378 ms</t>
   </si>
   <si>
     <t/>
@@ -53,7 +53,7 @@
     <t>TC_DeleteADM_02</t>
   </si>
   <si>
-    <t>2389 ms</t>
+    <t>4539 ms</t>
   </si>
 </sst>
 </file>
